--- a/results/intensive_linear_95p_weighted/original/log_intensive_linear_95p_weighted_b1_stage3_4_1000perm.xlsx
+++ b/results/intensive_linear_95p_weighted/original/log_intensive_linear_95p_weighted_b1_stage3_4_1000perm.xlsx
@@ -351,51 +351,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>total_reactions</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>non_ver</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fake</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>n_posts</t>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.0002054178475817995</v>
+        <v>-0.05671765060079959</v>
       </c>
       <c r="B2">
-        <v>-0.02520761608165049</v>
+        <v>-0.008916866550131356</v>
       </c>
       <c r="C2">
-        <v>0.0007811302435668723</v>
+        <v>-0.04360762336434614</v>
       </c>
       <c r="D2">
-        <v>0.003226641333477363</v>
+        <v>-0.02903057234811354</v>
       </c>
       <c r="E2">
-        <v>-0.03002715752924299</v>
+        <v>-0.02411852222553372</v>
+      </c>
+      <c r="F2">
+        <v>0.001849551807106874</v>
+      </c>
+      <c r="G2">
+        <v>-0.02384360552846322</v>
+      </c>
+      <c r="H2">
+        <v>0.001562653634133996</v>
+      </c>
+      <c r="I2">
+        <v>0.004278826122586133</v>
+      </c>
+      <c r="J2">
+        <v>-0.00230248044403367</v>
+      </c>
+      <c r="K2">
+        <v>-0.002144342177414278</v>
+      </c>
+      <c r="L2">
+        <v>-0.003033504158059744</v>
+      </c>
+      <c r="M2">
+        <v>0.00159514178958466</v>
+      </c>
+      <c r="N2">
+        <v>-0.0004780430281475144</v>
+      </c>
+      <c r="O2">
+        <v>-0.0001092884245577079</v>
+      </c>
+      <c r="P2">
+        <v>-0.0005868992793851915</v>
+      </c>
+      <c r="Q2">
+        <v>9.795589887294792e-05</v>
       </c>
     </row>
   </sheetData>
